--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487211_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487211_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0916</v>
+        <v>2.5096</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8952</v>
+        <v>0.5542</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1963</v>
+        <v>1.9554</v>
       </c>
       <c r="G2" t="n">
         <v>1.1467</v>
@@ -610,13 +610,13 @@
         <v>1.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8639</v>
+        <v>0.2819</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4429</v>
+        <v>0.1018</v>
       </c>
       <c r="U2" t="n">
-        <v>0.421</v>
+        <v>0.1801</v>
       </c>
       <c r="V2" t="n">
         <v>-0.8492</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>I. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0058</v>
+        <v>2.0248</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1181</v>
+        <v>-0.998</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8877</v>
+        <v>3.0228</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5919</v>
+        <v>1.3246</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5548</v>
+        <v>0.4492</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0371</v>
+        <v>0.8754</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1685</v>
+        <v>0.9638</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0464</v>
+        <v>-0.1915</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1221</v>
+        <v>1.1553</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7604</v>
+        <v>0.3609</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6012</v>
+        <v>0.6408</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1592</v>
+        <v>-0.2799</v>
       </c>
       <c r="P3" t="n">
         <v>-0.193</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7907</v>
+        <v>0.237</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2427</v>
+        <v>-0.0317</v>
       </c>
       <c r="U3" t="n">
-        <v>1.548</v>
+        <v>0.2687</v>
       </c>
       <c r="V3" t="n">
+        <v>0.6562</v>
+      </c>
+      <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="n">
-        <v>-0.3281</v>
-      </c>
       <c r="X3" t="n">
-        <v>0.3281</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. HANSEN GUTIERREZ</t>
+          <t>S. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9768</v>
+        <v>0.5783</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.8586</v>
+        <v>-1.3257</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8354</v>
+        <v>1.904</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3246</v>
+        <v>-3.6319</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4492</v>
+        <v>0.0496</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8754</v>
+        <v>-3.6815</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9638</v>
+        <v>-2.2709</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1915</v>
+        <v>0.3103</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1553</v>
+        <v>-2.5811</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3609</v>
+        <v>-1.361</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6408</v>
+        <v>-0.2607</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2799</v>
+        <v>-1.1003</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.193</v>
+        <v>2.1231</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7371</v>
+        <v>2.1231</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8110000000000001</v>
+        <v>0.2366</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8923</v>
+        <v>-0.2406</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0813</v>
+        <v>0.4772</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6562</v>
+        <v>1.8504</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1857</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6562</v>
+        <v>0.6647</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5407</v>
+        <v>0.4861</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1565</v>
+        <v>-1.2378</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6971</v>
+        <v>1.7239</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0562</v>
@@ -844,13 +844,13 @@
         <v>0.579</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0178</v>
+        <v>-0.0367</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2247</v>
+        <v>-0.306</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2426</v>
+        <v>0.2693</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. POPA ANDREI</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2531</v>
+        <v>0.2469</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.4573</v>
+        <v>-1.1054</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7105</v>
+        <v>1.3523</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1323</v>
+        <v>-0.5919</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.918</v>
+        <v>-0.5548</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0503</v>
+        <v>-0.0371</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1889</v>
+        <v>0.1685</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.532</v>
+        <v>0.0464</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3431</v>
+        <v>0.1221</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3212</v>
+        <v>-0.7604</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6139</v>
+        <v>-0.6012</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2928</v>
+        <v>-0.1592</v>
       </c>
       <c r="P6" t="n">
-        <v>0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9301</v>
+        <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7879</v>
+        <v>1.0318</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3372</v>
+        <v>0.0192</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4508</v>
+        <v>1.0126</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.6321</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.6406</v>
+        <v>-0.3281</v>
       </c>
       <c r="X6" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. HANSEN GUTIERREZ</t>
+          <t>J. RODRIGUEZ NERI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0587</v>
+        <v>0.029</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8453</v>
+        <v>-1.9508</v>
       </c>
       <c r="F7" t="n">
-        <v>1.904</v>
+        <v>1.9798</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.6319</v>
+        <v>2.5465</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0496</v>
+        <v>0.5216</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.6815</v>
+        <v>2.025</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.2709</v>
+        <v>2.1525</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3103</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.5811</v>
+        <v>1.2367</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.361</v>
+        <v>0.3941</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2607</v>
+        <v>-0.3942</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1003</v>
+        <v>0.7883</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1231</v>
+        <v>-3.8602</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-5.7902</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1231</v>
+        <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2829</v>
+        <v>-0.1712</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7601</v>
+        <v>-0.4408</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4772</v>
+        <v>0.2697</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8504</v>
+        <v>1.5138</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1857</v>
+        <v>2.1278</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6647</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ NERI</t>
+          <t>S. POPA ANDREI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5639</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3295</v>
+        <v>-2.9392</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7657</v>
+        <v>2.8711</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5465</v>
+        <v>0.1323</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5216</v>
+        <v>-0.918</v>
       </c>
       <c r="I8" t="n">
-        <v>2.025</v>
+        <v>1.0503</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1525</v>
+        <v>-0.1889</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9157999999999999</v>
+        <v>-1.532</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2367</v>
+        <v>1.3431</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3941</v>
+        <v>0.3212</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3942</v>
+        <v>0.6139</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7883</v>
+        <v>-0.2928</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.8602</v>
+        <v>0.965</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.7902</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
         <v>1.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7641</v>
+        <v>0.4667</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8196</v>
+        <v>-0.1447</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0555</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5138</v>
+        <v>-1.6321</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1278</v>
+        <v>-1.6406</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.614</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.527</v>
+        <v>-1.1274</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1231</v>
+        <v>-1.8038</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5961</v>
+        <v>0.6764</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3224</v>
@@ -1156,13 +1156,13 @@
         <v>0.386</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7185</v>
+        <v>-0.3189</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5354</v>
+        <v>-0.2161</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1831</v>
+        <v>-0.1028</v>
       </c>
       <c r="V9" t="n">
         <v>0.0929</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2734</v>
+        <v>-4.7667</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7274</v>
+        <v>-4.1672</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.546</v>
+        <v>-0.5995</v>
       </c>
       <c r="G10" t="n">
         <v>-2.735</v>
@@ -1234,13 +1234,13 @@
         <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3768</v>
+        <v>0.1299</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8923</v>
+        <v>-0.3321</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5155</v>
+        <v>0.462</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1616</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7621</v>
+        <v>-5.9223</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0286</v>
+        <v>-4.3494</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7335</v>
+        <v>-1.5729</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4888</v>
@@ -1312,13 +1312,13 @@
         <v>1.158</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2889</v>
+        <v>-0.4491</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4872</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1983</v>
+        <v>0.3589</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2123</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.199699999999999</v>
+        <v>-6.0098</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.513</v>
+        <v>-19.3231</v>
       </c>
       <c r="F12" t="n">
         <v>13.3133</v>
@@ -1363,7 +1363,7 @@
         <v>-1.270900000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.3457</v>
+        <v>-4.345700000000001</v>
       </c>
       <c r="K12" t="n">
         <v>-1.2327</v>
@@ -1372,7 +1372,7 @@
         <v>-3.1128</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3301999999999998</v>
+        <v>-0.3302000000000003</v>
       </c>
       <c r="N12" t="n">
         <v>-2.1724</v>
@@ -1390,10 +1390,10 @@
         <v>13.5105</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2181000000000002</v>
+        <v>1.408</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.5888</v>
+        <v>-2.399</v>
       </c>
       <c r="U12" t="n">
         <v>3.8071</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5624</v>
+        <v>7.6114</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2725</v>
+        <v>4.9735</v>
       </c>
       <c r="F13" t="n">
-        <v>2.29</v>
+        <v>2.638</v>
       </c>
       <c r="G13" t="n">
         <v>7.0307</v>
@@ -1468,13 +1468,13 @@
         <v>2.5091</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0596</v>
+        <v>-0.0106</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2942</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2346</v>
+        <v>0.5826</v>
       </c>
       <c r="V13" t="n">
         <v>0.2053</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.061</v>
+        <v>4.0342</v>
       </c>
       <c r="E14" t="n">
         <v>0.159</v>
       </c>
       <c r="F14" t="n">
-        <v>3.902</v>
+        <v>3.8752</v>
       </c>
       <c r="G14" t="n">
         <v>1.2073</v>
@@ -1546,13 +1546,13 @@
         <v>1.158</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4131</v>
+        <v>0.3863</v>
       </c>
       <c r="T14" t="n">
         <v>-0.0462</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4594</v>
+        <v>0.4326</v>
       </c>
       <c r="V14" t="n">
         <v>1.4755</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5569</v>
+        <v>2.4835</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2216</v>
+        <v>-1.3217</v>
       </c>
       <c r="F15" t="n">
-        <v>3.7785</v>
+        <v>3.8052</v>
       </c>
       <c r="G15" t="n">
         <v>0.3424</v>
@@ -1624,13 +1624,13 @@
         <v>1.158</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0258</v>
+        <v>-0.0992</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2842</v>
+        <v>-0.3843</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2584</v>
+        <v>0.2852</v>
       </c>
       <c r="V15" t="n">
         <v>2.0473</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4979</v>
+        <v>1.4583</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4736</v>
+        <v>0.2734</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0243</v>
+        <v>1.1849</v>
       </c>
       <c r="G16" t="n">
         <v>0.1151</v>
@@ -1702,13 +1702,13 @@
         <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4178</v>
+        <v>0.3781</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3252</v>
+        <v>0.1249</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0925</v>
+        <v>0.2531</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2164</v>
+        <v>0.9963</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6622</v>
+        <v>0.3618</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5542</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>0.5548</v>
@@ -1780,13 +1780,13 @@
         <v>0.193</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6617</v>
+        <v>0.4415</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5486</v>
+        <v>0.2482</v>
       </c>
       <c r="U17" t="n">
-        <v>0.113</v>
+        <v>0.1933</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ ORTEGA</t>
+          <t>A. JUSTO ANTOLIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2008</v>
+        <v>-0.0848</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.7481</v>
+        <v>-2.3914</v>
       </c>
       <c r="F18" t="n">
-        <v>5.9489</v>
+        <v>2.3066</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5659</v>
+        <v>0.1766</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1682</v>
+        <v>1.8031</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3977</v>
+        <v>-1.6265</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1095</v>
+        <v>0.1423</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6143</v>
+        <v>1.4696</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5048</v>
+        <v>-1.3273</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4564</v>
+        <v>0.0343</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.3335</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9025</v>
+        <v>-0.2992</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1231</v>
+        <v>0.772</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.0532</v>
+        <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9301</v>
+        <v>1.7371</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3986</v>
+        <v>-0.4194</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.9125</v>
       </c>
       <c r="U18" t="n">
-        <v>1.9062</v>
+        <v>0.4931</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.6406</v>
+        <v>-0.614</v>
       </c>
       <c r="W18" t="n">
-        <v>-2.2968</v>
+        <v>-0.6562</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6562</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>A. FERNANDEZ ORTEGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2449</v>
+        <v>-0.5021</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9333</v>
+        <v>-5.6479</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6884</v>
+        <v>5.1458</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.3535</v>
+        <v>2.5659</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8133</v>
+        <v>2.1682</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5401</v>
+        <v>0.3977</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.9207</v>
+        <v>1.1095</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.5527</v>
+        <v>1.6143</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.368</v>
+        <v>-0.5048</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4328</v>
+        <v>1.4564</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2607</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1721</v>
+        <v>0.9025</v>
       </c>
       <c r="P19" t="n">
-        <v>1.158</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.965</v>
+        <v>-4.0532</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1231</v>
+        <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8031</v>
+        <v>0.6957</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3385</v>
+        <v>-0.4075</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4646</v>
+        <v>1.1031</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1474</v>
+        <v>-1.6406</v>
       </c>
       <c r="W19" t="n">
-        <v>0.614</v>
+        <v>-2.2968</v>
       </c>
       <c r="X19" t="n">
-        <v>0.5334</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. JUSTO ANTOLIN</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7996</v>
+        <v>-1.2473</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8921</v>
+        <v>-3.5341</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0925</v>
+        <v>2.2868</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1766</v>
+        <v>-3.3535</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8031</v>
+        <v>-1.8133</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6265</v>
+        <v>-1.5401</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1423</v>
+        <v>-2.9207</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4696</v>
+        <v>-1.5527</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3273</v>
+        <v>-1.368</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0343</v>
+        <v>-0.4328</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3335</v>
+        <v>-0.2607</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2992</v>
+        <v>-0.1721</v>
       </c>
       <c r="P20" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7371</v>
+        <v>2.1231</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1343</v>
+        <v>-0.1993</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4132</v>
+        <v>-0.2624</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2789</v>
+        <v>0.0631</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.614</v>
+        <v>1.1474</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6562</v>
+        <v>0.614</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0422</v>
+        <v>0.5334</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5395</v>
+        <v>-1.359</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1021</v>
+        <v>-1.002</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4374</v>
+        <v>-0.357</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0735</v>
@@ -2092,13 +2092,13 @@
         <v>0.193</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.659</v>
+        <v>-0.4786</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4759</v>
+        <v>-0.3758</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1831</v>
+        <v>-0.1028</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.19</v>
+        <v>-2.1692</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3034</v>
+        <v>-1.6038</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8866000000000001</v>
+        <v>-0.5654</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2759</v>
@@ -2170,13 +2170,13 @@
         <v>0.772</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2472</v>
+        <v>-0.2264</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2247</v>
+        <v>-0.5251</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0225</v>
+        <v>0.2987</v>
       </c>
       <c r="V22" t="n">
         <v>0.4912</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1218</v>
+        <v>-4.0217</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.68</v>
+        <v>-3.5798</v>
       </c>
       <c r="F23" t="n">
         <v>-0.4418</v>
@@ -2248,10 +2248,10 @@
         <v>0.579</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7866</v>
+        <v>-0.6864</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7733</v>
+        <v>-0.6732</v>
       </c>
       <c r="U23" t="n">
         <v>-0.0132</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.1996</v>
+        <v>7.199599999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-13.3133</v>
+        <v>-13.313</v>
       </c>
       <c r="F24" t="n">
-        <v>20.513</v>
+        <v>20.5129</v>
       </c>
       <c r="G24" t="n">
         <v>4.676099999999998</v>
@@ -2326,10 +2326,10 @@
         <v>13.5104</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2182000000000003</v>
+        <v>-0.2183000000000002</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.807</v>
+        <v>-3.8071</v>
       </c>
       <c r="U24" t="n">
         <v>3.5888</v>
@@ -2338,7 +2338,7 @@
         <v>2.7417</v>
       </c>
       <c r="W24" t="n">
-        <v>3.674199999999999</v>
+        <v>3.6742</v>
       </c>
       <c r="X24" t="n">
         <v>-0.9323000000000001</v>
